--- a/tiflow/develop/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/develop/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/tiflow-core/StructureDefinition/ti-feature-definition</t>
+    <t>https://gematik.de/fhir/tiflow/StructureDefinition/ti-feature-definition</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T06:36:31+00:00</t>
+    <t>2026-05-22T12:36:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow/develop/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/develop/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-22T12:36:03+00:00</t>
+    <t>2026-05-22T13:53:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow/develop/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/develop/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-22T13:53:02+00:00</t>
+    <t>2026-05-26T05:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow/develop/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/develop/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T05:55:50+00:00</t>
+    <t>2026-05-26T07:11:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow/develop/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/develop/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T07:11:01+00:00</t>
+    <t>2026-05-26T07:59:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow/develop/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/develop/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T07:59:08+00:00</t>
+    <t>2026-05-26T08:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow/develop/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow/develop/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T08:55:00+00:00</t>
+    <t>2026-05-29T06:02:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
